--- a/docs/all/idx9_infnin_loadings_y_tops.xlsx
+++ b/docs/all/idx9_infnin_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.4217763905429527</v>
+        <v>0.4217763905429536</v>
       </c>
       <c r="D2">
-        <v>0.1504356838633102</v>
+        <v>0.1504356838633105</v>
       </c>
       <c r="E2">
         <v>15</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.3068382714595461</v>
+        <v>0.306838271459547</v>
       </c>
       <c r="D3">
-        <v>0.1094405145414418</v>
+        <v>0.1094405145414421</v>
       </c>
       <c r="E3">
         <v>10.9</v>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.009622362482477848</v>
+        <v>0.009622362482477432</v>
       </c>
       <c r="D4">
-        <v>0.003432023965515917</v>
+        <v>0.003432023965515769</v>
       </c>
       <c r="E4">
         <v>0.3</v>
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.07712735392209487</v>
+        <v>-0.07712735392209447</v>
       </c>
       <c r="D5">
-        <v>0.02750914108042354</v>
+        <v>0.0275091410804234</v>
       </c>
       <c r="E5">
         <v>2.8</v>
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.4277317691593429</v>
+        <v>-0.4277317691593427</v>
       </c>
       <c r="D6">
-        <v>0.1525597986191606</v>
+        <v>0.1525597986191605</v>
       </c>
       <c r="E6">
         <v>15.3</v>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.3479836458610875</v>
+        <v>-0.3479836458610874</v>
       </c>
       <c r="D7">
         <v>0.124115903384188</v>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.4279701372342439</v>
+        <v>-0.4279701372342429</v>
       </c>
       <c r="D8">
-        <v>0.1526448177552786</v>
+        <v>0.1526448177552782</v>
       </c>
       <c r="E8">
         <v>15.3</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.0872433337405719</v>
+        <v>-0.08724333374057207</v>
       </c>
       <c r="D9">
-        <v>0.03111722435881904</v>
+        <v>0.03111722435881911</v>
       </c>
       <c r="E9">
         <v>3.1</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.03261335495786311</v>
+        <v>-0.03261335495786359</v>
       </c>
       <c r="D10">
-        <v>0.01163225933496953</v>
+        <v>0.0116322593349697</v>
       </c>
       <c r="E10">
         <v>1.2</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.2821037769312924</v>
+        <v>-0.2821037769312917</v>
       </c>
       <c r="D11">
-        <v>0.1006184214067806</v>
+        <v>0.1006184214067804</v>
       </c>
       <c r="E11">
         <v>10.1</v>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.4175107227959658</v>
+        <v>-0.4175107227959651</v>
       </c>
       <c r="D13">
-        <v>0.1484357436525198</v>
+        <v>0.1484357436525196</v>
       </c>
       <c r="E13">
         <v>14.8</v>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="C14">
-        <v>-0.5686319028350156</v>
+        <v>-0.5686319028350157</v>
       </c>
       <c r="D14">
-        <v>0.202163189478396</v>
+        <v>0.2021631894783962</v>
       </c>
       <c r="E14">
         <v>20.2</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>0.1990559648130767</v>
+        <v>0.1990559648130769</v>
       </c>
       <c r="D15">
-        <v>0.07076948818854228</v>
+        <v>0.07076948818854238</v>
       </c>
       <c r="E15">
         <v>7.1</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.27564179511722</v>
+        <v>-0.2756417951172191</v>
       </c>
       <c r="D16">
-        <v>0.09799771025266563</v>
+        <v>0.09799771025266535</v>
       </c>
       <c r="E16">
         <v>9.800000000000001</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C17">
-        <v>-0.05457360636486595</v>
+        <v>-0.05457360636486649</v>
       </c>
       <c r="D17">
-        <v>0.01940231328747813</v>
+        <v>0.01940231328747833</v>
       </c>
       <c r="E17">
         <v>1.9</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.2609491248307983</v>
+        <v>-0.2609491248307991</v>
       </c>
       <c r="D18">
-        <v>0.0927740900648984</v>
+        <v>0.09277409006489871</v>
       </c>
       <c r="E18">
         <v>9.300000000000001</v>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.257546166379183</v>
+        <v>-0.2575461663791829</v>
       </c>
       <c r="D19">
-        <v>0.09156425127321068</v>
+        <v>0.09156425127321069</v>
       </c>
       <c r="E19">
         <v>9.199999999999999</v>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.08620369356542516</v>
+        <v>0.08620369356542434</v>
       </c>
       <c r="D20">
-        <v>0.03064761851932359</v>
+        <v>0.03064761851932331</v>
       </c>
       <c r="E20">
         <v>3.1</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.2729876985051061</v>
+        <v>0.272987698505105</v>
       </c>
       <c r="D21">
-        <v>0.09705411100398886</v>
+        <v>0.0970541110039885</v>
       </c>
       <c r="E21">
         <v>9.699999999999999</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.4089882430616423</v>
+        <v>-0.4089882430616426</v>
       </c>
       <c r="D22">
-        <v>0.1454057840657188</v>
+        <v>0.145405784065719</v>
       </c>
       <c r="E22">
         <v>14.5</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>-0.01064817943059642</v>
+        <v>-0.01064817943059745</v>
       </c>
       <c r="D23">
-        <v>0.003785700213257654</v>
+        <v>0.003785700213258022</v>
       </c>
       <c r="E23">
         <v>0.4</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.021631963654936</v>
+        <v>0.02163196365493535</v>
       </c>
       <c r="D24">
-        <v>0.009120520406710913</v>
+        <v>0.009120520406710658</v>
       </c>
       <c r="E24">
         <v>0.9</v>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.0966002363943866</v>
+        <v>0.09660023639438582</v>
       </c>
       <c r="D25">
-        <v>0.04072882339218723</v>
+        <v>0.04072882339218698</v>
       </c>
       <c r="E25">
         <v>4.1</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="C26">
-        <v>-0.229747611934174</v>
+        <v>-0.2297476119341727</v>
       </c>
       <c r="D26">
-        <v>0.09686673925973428</v>
+        <v>0.09686673925973391</v>
       </c>
       <c r="E26">
         <v>9.699999999999999</v>
@@ -924,7 +924,7 @@
         <v>0.1021095186285826</v>
       </c>
       <c r="D27">
-        <v>0.04305166018337464</v>
+        <v>0.04305166018337474</v>
       </c>
       <c r="E27">
         <v>4.3</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.2926965157205372</v>
+        <v>-0.2926965157205376</v>
       </c>
       <c r="D28">
-        <v>0.1234074070752797</v>
+        <v>0.1234074070752801</v>
       </c>
       <c r="E28">
         <v>12.3</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="C29">
-        <v>-0.00630873121814524</v>
+        <v>-0.006308731218145468</v>
       </c>
       <c r="D29">
-        <v>0.002659902389509544</v>
+        <v>0.002659902389509645</v>
       </c>
       <c r="E29">
         <v>0.3</v>
@@ -987,7 +987,7 @@
         <v>-0.05136688957913933</v>
       </c>
       <c r="D30">
-        <v>0.02165743120268721</v>
+        <v>0.02165743120268725</v>
       </c>
       <c r="E30">
         <v>2.2</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.6474215124529392</v>
+        <v>0.6474215124529391</v>
       </c>
       <c r="D31">
-        <v>0.2729674111080207</v>
+        <v>0.2729674111080211</v>
       </c>
       <c r="E31">
         <v>27.3</v>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.5866952279368165</v>
+        <v>0.5866952279368155</v>
       </c>
       <c r="D32">
         <v>0.2473638493607888</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.2645711278346457</v>
+        <v>0.2645711278346449</v>
       </c>
       <c r="D33">
-        <v>0.1115491135679586</v>
+        <v>0.1115491135679585</v>
       </c>
       <c r="E33">
         <v>11.2</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.07264116456268901</v>
+        <v>0.07264116456268847</v>
       </c>
       <c r="D34">
-        <v>0.03062714205374856</v>
+        <v>0.03062714205374839</v>
       </c>
       <c r="E34">
         <v>3.1</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.08369336220065933</v>
+        <v>-0.08369336220065882</v>
       </c>
       <c r="D35">
-        <v>0.03800903206190341</v>
+        <v>0.03800903206190315</v>
       </c>
       <c r="E35">
         <v>3.8</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.08051700998733535</v>
+        <v>-0.08051700998733444</v>
       </c>
       <c r="D36">
-        <v>0.03656650340799807</v>
+        <v>0.03656650340799764</v>
       </c>
       <c r="E36">
         <v>3.7</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.6595390434221995</v>
+        <v>0.659539043422201</v>
       </c>
       <c r="D37">
-        <v>0.2995272263935168</v>
+        <v>0.2995272263935173</v>
       </c>
       <c r="E37">
         <v>30</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.6374893248369403</v>
+        <v>0.6374893248369391</v>
       </c>
       <c r="D38">
-        <v>0.2895134279437221</v>
+        <v>0.2895134279437214</v>
       </c>
       <c r="E38">
         <v>29</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.04625972024667148</v>
+        <v>-0.04625972024667169</v>
       </c>
       <c r="D39">
-        <v>0.02100868149871708</v>
+        <v>0.02100868149871716</v>
       </c>
       <c r="E39">
         <v>2.1</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="C40">
-        <v>0.03003372295684949</v>
+        <v>0.03003372295685122</v>
       </c>
       <c r="D40">
-        <v>0.01363970461681636</v>
+        <v>0.01363970461681713</v>
       </c>
       <c r="E40">
         <v>1.4</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.03222706788581216</v>
+        <v>-0.03222706788581304</v>
       </c>
       <c r="D41">
-        <v>0.01463580413457595</v>
+        <v>0.01463580413457634</v>
       </c>
       <c r="E41">
         <v>1.5</v>
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.1593189583880648</v>
+        <v>0.1593189583880645</v>
       </c>
       <c r="D42">
-        <v>0.07235411791585671</v>
+        <v>0.07235411791585654</v>
       </c>
       <c r="E42">
         <v>7.2</v>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="C43">
-        <v>-0.0464023202621889</v>
+        <v>-0.04640232026218924</v>
       </c>
       <c r="D43">
-        <v>0.02107344277033184</v>
+        <v>0.02107344277033198</v>
       </c>
       <c r="E43">
         <v>2.1</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.106970475048198</v>
+        <v>0.1069704750481983</v>
       </c>
       <c r="D44">
-        <v>0.0485802470933826</v>
+        <v>0.04858024709338269</v>
       </c>
       <c r="E44">
         <v>4.9</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="C45">
-        <v>-0.3194825263623111</v>
+        <v>-0.31948252636231</v>
       </c>
       <c r="D45">
-        <v>0.1450918121631792</v>
+        <v>0.1450918121631786</v>
       </c>
       <c r="E45">
         <v>14.5</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="C46">
-        <v>-0.3333816057757547</v>
+        <v>-0.3333816057757544</v>
       </c>
       <c r="D46">
-        <v>0.113670408396599</v>
+        <v>0.1136704083965989</v>
       </c>
       <c r="E46">
         <v>11.4</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="C47">
-        <v>-0.1895708363539436</v>
+        <v>-0.1895708363539444</v>
       </c>
       <c r="D47">
-        <v>0.06463642269133477</v>
+        <v>0.06463642269133502</v>
       </c>
       <c r="E47">
         <v>6.5</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="C48">
-        <v>-0.530481493319294</v>
+        <v>-0.5304814933192928</v>
       </c>
       <c r="D48">
-        <v>0.1808739502952721</v>
+        <v>0.1808739502952716</v>
       </c>
       <c r="E48">
         <v>18.1</v>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.1824430158719459</v>
+        <v>-0.182443015871946</v>
       </c>
       <c r="D50">
         <v>0.06220610784753589</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.4847466492255482</v>
+        <v>-0.4847466492255468</v>
       </c>
       <c r="D51">
-        <v>0.1652801133347899</v>
+        <v>0.1652801133347894</v>
       </c>
       <c r="E51">
         <v>16.5</v>
@@ -1449,7 +1449,7 @@
         <v>0.1610262610181556</v>
       </c>
       <c r="D52">
-        <v>0.05490381153429031</v>
+        <v>0.05490381153429026</v>
       </c>
       <c r="E52">
         <v>5.5</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C53">
-        <v>-0.06415807384038835</v>
+        <v>-0.06415807384038846</v>
       </c>
       <c r="D53">
-        <v>0.02187545542114153</v>
+        <v>0.02187545542114155</v>
       </c>
       <c r="E53">
         <v>2.2</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.2760677701081725</v>
+        <v>-0.276067770108173</v>
       </c>
       <c r="D54">
-        <v>0.09412857707105252</v>
+        <v>0.09412857707105267</v>
       </c>
       <c r="E54">
         <v>9.4</v>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.1367976990530131</v>
+        <v>0.1367976990530141</v>
       </c>
       <c r="D55">
-        <v>0.04664279627212088</v>
+        <v>0.04664279627212121</v>
       </c>
       <c r="E55">
         <v>4.7</v>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="C56">
-        <v>-0.205203133785198</v>
+        <v>-0.2052031337852001</v>
       </c>
       <c r="D56">
-        <v>0.06996643971207891</v>
+        <v>0.06996643971207961</v>
       </c>
       <c r="E56">
         <v>7</v>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C57">
-        <v>-0.1265871784500406</v>
+        <v>-0.1265871784500417</v>
       </c>
       <c r="D57">
-        <v>0.05381947967589582</v>
+        <v>0.05381947967589625</v>
       </c>
       <c r="E57">
         <v>5.4</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="C58">
-        <v>-0.004328147522226306</v>
+        <v>-0.004328147522227412</v>
       </c>
       <c r="D58">
-        <v>0.001840144084565958</v>
+        <v>0.001840144084566427</v>
       </c>
       <c r="E58">
         <v>0.2</v>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.01498166518511046</v>
+        <v>0.01498166518511001</v>
       </c>
       <c r="D59">
-        <v>0.006369566292682225</v>
+        <v>0.00636956629268203</v>
       </c>
       <c r="E59">
         <v>0.6</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="C60">
-        <v>-0.4806699651366268</v>
+        <v>-0.4806699651366275</v>
       </c>
       <c r="D60">
-        <v>0.2043604078725395</v>
+        <v>0.2043604078725396</v>
       </c>
       <c r="E60">
         <v>20.4</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C61">
-        <v>0.005998688327583345</v>
+        <v>0.005998688327580258</v>
       </c>
       <c r="D61">
-        <v>0.002550386922920643</v>
+        <v>0.002550386922919328</v>
       </c>
       <c r="E61">
         <v>0.3</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="C62">
-        <v>0.1878592434840628</v>
+        <v>0.1878592434840684</v>
       </c>
       <c r="D62">
-        <v>0.07986975348068075</v>
+        <v>0.07986975348068305</v>
       </c>
       <c r="E62">
         <v>8</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="C63">
-        <v>0.3163308219636298</v>
+        <v>0.3163308219636256</v>
       </c>
       <c r="D63">
-        <v>0.1344903998334243</v>
+        <v>0.1344903998334224</v>
       </c>
       <c r="E63">
         <v>13.4</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.2365623754823402</v>
+        <v>0.2365623754823396</v>
       </c>
       <c r="D64">
-        <v>0.1005762519967864</v>
+        <v>0.100576251996786</v>
       </c>
       <c r="E64">
         <v>10.1</v>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="C65">
-        <v>-0.1080089217820166</v>
+        <v>-0.1080089217820188</v>
       </c>
       <c r="D65">
-        <v>0.04592079578546605</v>
+        <v>0.04592079578546694</v>
       </c>
       <c r="E65">
         <v>4.6</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="C66">
-        <v>0.1433334910890963</v>
+        <v>0.1433334910890968</v>
       </c>
       <c r="D66">
-        <v>0.06093929894795234</v>
+        <v>0.0609392989479525</v>
       </c>
       <c r="E66">
         <v>6.1</v>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="C67">
-        <v>-0.7274094066071236</v>
+        <v>-0.7274094066071227</v>
       </c>
       <c r="D67">
-        <v>0.3092635151070861</v>
+        <v>0.3092635151070854</v>
       </c>
       <c r="E67">
         <v>30.9</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C68">
-        <v>0.2049908411770195</v>
+        <v>0.2049908411770175</v>
       </c>
       <c r="D68">
-        <v>0.083036906833344</v>
+        <v>0.08303690683334317</v>
       </c>
       <c r="E68">
         <v>8.300000000000001</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.1649166438687656</v>
+        <v>0.1649166438687647</v>
       </c>
       <c r="D69">
-        <v>0.06680380408007053</v>
+        <v>0.06680380408007014</v>
       </c>
       <c r="E69">
         <v>6.7</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="C70">
-        <v>0.1740527641643282</v>
+        <v>0.1740527641643286</v>
       </c>
       <c r="D70">
-        <v>0.07050462878738382</v>
+        <v>0.07050462878738399</v>
       </c>
       <c r="E70">
         <v>7.1</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="C71">
-        <v>-0.08010128442449552</v>
+        <v>-0.08010128442449965</v>
       </c>
       <c r="D71">
-        <v>0.03244712228993807</v>
+        <v>0.03244712228993973</v>
       </c>
       <c r="E71">
         <v>3.2</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="C72">
-        <v>0.5586598632827418</v>
+        <v>0.5586598632827422</v>
       </c>
       <c r="D72">
-        <v>0.2262998032135409</v>
+        <v>0.226299803213541</v>
       </c>
       <c r="E72">
         <v>22.6</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="C73">
-        <v>-0.6781734298149656</v>
+        <v>-0.678173429814965</v>
       </c>
       <c r="D73">
-        <v>0.274711902175987</v>
+        <v>0.2747119021759866</v>
       </c>
       <c r="E73">
         <v>27.5</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.2677699768266599</v>
+        <v>0.2677699768266592</v>
       </c>
       <c r="D74">
-        <v>0.1084672392720279</v>
+        <v>0.1084672392720275</v>
       </c>
       <c r="E74">
         <v>10.8</v>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="C75">
-        <v>0.1722831503387198</v>
+        <v>0.1722831503387215</v>
       </c>
       <c r="D75">
-        <v>0.06978780037922509</v>
+        <v>0.06978780037922576</v>
       </c>
       <c r="E75">
         <v>7</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="C76">
-        <v>0.1421769251168112</v>
+        <v>0.1421769251168088</v>
       </c>
       <c r="D76">
-        <v>0.05759248567881619</v>
+        <v>0.05759248567881521</v>
       </c>
       <c r="E76">
         <v>5.8</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.02076688669509402</v>
+        <v>0.02076688669509984</v>
       </c>
       <c r="D77">
-        <v>0.008412171128318924</v>
+        <v>0.00841217112832128</v>
       </c>
       <c r="E77">
         <v>0.8</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.004779684064394214</v>
+        <v>0.004779684064388952</v>
       </c>
       <c r="D78">
-        <v>0.001936136161347753</v>
+        <v>0.00193613616134562</v>
       </c>
       <c r="E78">
         <v>0.2</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="C79">
-        <v>0.06543081784326642</v>
+        <v>0.06543081784326688</v>
       </c>
       <c r="D79">
-        <v>0.02766277103760767</v>
+        <v>0.02766277103760788</v>
       </c>
       <c r="E79">
         <v>2.8</v>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.09325488668602032</v>
+        <v>0.09325488668602123</v>
       </c>
       <c r="D80">
-        <v>0.03942620104050721</v>
+        <v>0.03942620104050762</v>
       </c>
       <c r="E80">
         <v>3.9</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.1324358045457752</v>
+        <v>-0.1324358045457757</v>
       </c>
       <c r="D81">
-        <v>0.05599106749829755</v>
+        <v>0.05599106749829779</v>
       </c>
       <c r="E81">
         <v>5.6</v>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.2649275905785187</v>
+        <v>0.2649275905785188</v>
       </c>
       <c r="D82">
-        <v>0.1120058027896533</v>
+        <v>0.1120058027896535</v>
       </c>
       <c r="E82">
         <v>11.2</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.06020889727523894</v>
+        <v>-0.06020889727523287</v>
       </c>
       <c r="D83">
-        <v>0.02545505305682464</v>
+        <v>0.02545505305682209</v>
       </c>
       <c r="E83">
         <v>2.5</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="C84">
-        <v>0.1674016612141806</v>
+        <v>0.1674016612141777</v>
       </c>
       <c r="D84">
-        <v>0.07077389490340304</v>
+        <v>0.07077389490340187</v>
       </c>
       <c r="E84">
         <v>7.1</v>
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="C85">
-        <v>0.538275724565783</v>
+        <v>0.5382757245657831</v>
       </c>
       <c r="D85">
-        <v>0.2275716338963353</v>
+        <v>0.2275716338963354</v>
       </c>
       <c r="E85">
         <v>22.8</v>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="C86">
-        <v>0.002573651838163888</v>
+        <v>0.002573651838166953</v>
       </c>
       <c r="D86">
-        <v>0.001088085765643115</v>
+        <v>0.001088085765644412</v>
       </c>
       <c r="E86">
         <v>0.1</v>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="C87">
-        <v>0.2348516671202601</v>
+        <v>0.2348516671202598</v>
       </c>
       <c r="D87">
-        <v>0.0992903361059973</v>
+        <v>0.09929033610599725</v>
       </c>
       <c r="E87">
         <v>9.9</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C88">
-        <v>-0.7175931197656724</v>
+        <v>-0.7175931197656723</v>
       </c>
       <c r="D88">
-        <v>0.3033832500426744</v>
+        <v>0.3033832500426745</v>
       </c>
       <c r="E88">
         <v>30.3</v>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="C89">
-        <v>-0.08834854666006733</v>
+        <v>-0.08834854666007044</v>
       </c>
       <c r="D89">
-        <v>0.03735190386305638</v>
+        <v>0.03735190386305771</v>
       </c>
       <c r="E89">
         <v>3.7</v>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="C90">
-        <v>0.009853215263126158</v>
+        <v>0.009853215263126479</v>
       </c>
       <c r="D90">
-        <v>0.00359627506679723</v>
+        <v>0.003596275066797364</v>
       </c>
       <c r="E90">
         <v>0.4</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="C91">
-        <v>-0.01477167019062964</v>
+        <v>-0.01477167019062868</v>
       </c>
       <c r="D91">
-        <v>0.005391436986088819</v>
+        <v>0.005391436986088495</v>
       </c>
       <c r="E91">
         <v>0.5</v>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.3477321328138399</v>
+        <v>0.3477321328138404</v>
       </c>
       <c r="D92">
-        <v>0.1269169875789228</v>
+        <v>0.1269169875789236</v>
       </c>
       <c r="E92">
         <v>12.7</v>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="C93">
-        <v>-0.2094231399069116</v>
+        <v>-0.2094231399069119</v>
       </c>
       <c r="D93">
-        <v>0.07643628971307607</v>
+        <v>0.07643628971307653</v>
       </c>
       <c r="E93">
         <v>7.6</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="C94">
-        <v>-0.5841281475477667</v>
+        <v>-0.5841281475477687</v>
       </c>
       <c r="D94">
-        <v>0.2131979700780429</v>
+        <v>0.2131979700780446</v>
       </c>
       <c r="E94">
         <v>21.3</v>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="C95">
-        <v>-0.2150472811539693</v>
+        <v>-0.2150472811539691</v>
       </c>
       <c r="D95">
-        <v>0.07848901650314545</v>
+        <v>0.07848901650314574</v>
       </c>
       <c r="E95">
         <v>7.8</v>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="C96">
-        <v>0.4926866116644109</v>
+        <v>0.4926866116644145</v>
       </c>
       <c r="D96">
-        <v>0.1798231876557393</v>
+        <v>0.1798231876557415</v>
       </c>
       <c r="E96">
         <v>18</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="C97">
-        <v>-0.2902347966902996</v>
+        <v>-0.2902347966902915</v>
       </c>
       <c r="D97">
-        <v>0.1059313264737433</v>
+        <v>0.1059313264737408</v>
       </c>
       <c r="E97">
         <v>10.6</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C98">
-        <v>0.11073006889048</v>
+        <v>0.1107300688904727</v>
       </c>
       <c r="D98">
-        <v>0.04041480625982281</v>
+        <v>0.04041480625982034</v>
       </c>
       <c r="E98">
         <v>4</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="C99">
-        <v>0.2324379229068941</v>
+        <v>0.2324379229068881</v>
       </c>
       <c r="D99">
-        <v>0.08483633863724074</v>
+        <v>0.08483633863723893</v>
       </c>
       <c r="E99">
         <v>8.5</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.2327941743574098</v>
+        <v>0.232794174357413</v>
       </c>
       <c r="D100">
-        <v>0.08496636504738063</v>
+        <v>0.0849663650473822</v>
       </c>
       <c r="E100">
         <v>8.5</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="C101">
-        <v>0.03054534155824214</v>
+        <v>0.03054534155824219</v>
       </c>
       <c r="D101">
-        <v>0.01276843558351415</v>
+        <v>0.01276843558351427</v>
       </c>
       <c r="E101">
         <v>1.3</v>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.02068873657668646</v>
+        <v>0.0206887365766865</v>
       </c>
       <c r="D102">
-        <v>0.008648218903691855</v>
+        <v>0.008648218903691942</v>
       </c>
       <c r="E102">
         <v>0.9</v>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="C103">
-        <v>0.108423857347117</v>
+        <v>0.1084238573471119</v>
       </c>
       <c r="D103">
-        <v>0.04532288616295511</v>
+        <v>0.04532288616295339</v>
       </c>
       <c r="E103">
         <v>4.5</v>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="C104">
-        <v>-0.1045957267237841</v>
+        <v>-0.1045957267237809</v>
       </c>
       <c r="D104">
-        <v>0.04372266705340275</v>
+        <v>0.04372266705340173</v>
       </c>
       <c r="E104">
         <v>4.4</v>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="C105">
-        <v>-0.1897389229061295</v>
+        <v>-0.1897389229061219</v>
       </c>
       <c r="D105">
-        <v>0.07931386886582566</v>
+        <v>0.07931386886582312</v>
       </c>
       <c r="E105">
         <v>7.9</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="C106">
-        <v>-0.05350337974898534</v>
+        <v>-0.05350337974898303</v>
       </c>
       <c r="D106">
-        <v>0.02236525843139172</v>
+        <v>0.02236525843139093</v>
       </c>
       <c r="E106">
         <v>2.2</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.08270110595236198</v>
+        <v>0.08270110595235557</v>
       </c>
       <c r="D107">
-        <v>0.03457036949561229</v>
+        <v>0.0345703694956099</v>
       </c>
       <c r="E107">
         <v>3.5</v>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.6037684212486377</v>
+        <v>0.6037684212486408</v>
       </c>
       <c r="D108">
-        <v>0.2523847434926809</v>
+        <v>0.2523847434926842</v>
       </c>
       <c r="E108">
         <v>25.2</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="C109">
-        <v>-0.6337278414939299</v>
+        <v>-0.633727841493931</v>
       </c>
       <c r="D109">
-        <v>0.2649082547060699</v>
+        <v>0.2649082547060725</v>
       </c>
       <c r="E109">
         <v>26.5</v>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="C110">
-        <v>-0.2336576250624202</v>
+        <v>-0.2336576250624231</v>
       </c>
       <c r="D110">
-        <v>0.09767258056413457</v>
+        <v>0.09767258056413661</v>
       </c>
       <c r="E110">
         <v>9.800000000000001</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="C111">
-        <v>0.3309030773953645</v>
+        <v>0.3309030773953621</v>
       </c>
       <c r="D111">
-        <v>0.1383227167407213</v>
+        <v>0.1383227167407214</v>
       </c>
       <c r="E111">
         <v>13.8</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="C112">
-        <v>0.6825077307645204</v>
+        <v>0.6825077307645209</v>
       </c>
       <c r="D112">
-        <v>0.3567047633866368</v>
+        <v>0.356704763386637</v>
       </c>
       <c r="E112">
         <v>35.7</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.7029917534673978</v>
+        <v>-0.7029917534673981</v>
       </c>
       <c r="D113">
-        <v>0.3674105006875925</v>
+        <v>0.3674105006875926</v>
       </c>
       <c r="E113">
         <v>36.7</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="C114">
-        <v>-0.101815406037879</v>
+        <v>-0.1018154060378785</v>
       </c>
       <c r="D114">
-        <v>0.05321264314350522</v>
+        <v>0.05321264314350498</v>
       </c>
       <c r="E114">
         <v>5.3</v>
@@ -2772,7 +2772,7 @@
         <v>0.05143974391419372</v>
       </c>
       <c r="D115">
-        <v>0.02688438658566987</v>
+        <v>0.02688438658566988</v>
       </c>
       <c r="E115">
         <v>2.7</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="C116">
-        <v>0.001448802419427833</v>
+        <v>0.00144880241942788</v>
       </c>
       <c r="D116">
-        <v>0.0007571998102308633</v>
+        <v>0.0007571998102308881</v>
       </c>
       <c r="E116">
         <v>0.1</v>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="C117">
-        <v>0.05049990792757456</v>
+        <v>0.05049990792757469</v>
       </c>
       <c r="D117">
-        <v>0.026393192188716</v>
+        <v>0.02639319218871607</v>
       </c>
       <c r="E117">
         <v>2.6</v>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="C118">
-        <v>0.09908915441254731</v>
+        <v>0.09908915441254751</v>
       </c>
       <c r="D118">
-        <v>0.05178779929615855</v>
+        <v>0.05178779929615866</v>
       </c>
       <c r="E118">
         <v>5.2</v>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="C119">
-        <v>0.04337869789072279</v>
+        <v>0.04337869789072273</v>
       </c>
       <c r="D119">
-        <v>0.02267137421256451</v>
+        <v>0.02267137421256448</v>
       </c>
       <c r="E119">
         <v>2.3</v>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="C120">
-        <v>-0.03047244707659816</v>
+        <v>-0.03047244707659778</v>
       </c>
       <c r="D120">
-        <v>0.01592607165356787</v>
+        <v>0.01592607165356767</v>
       </c>
       <c r="E120">
         <v>1.6</v>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="C121">
-        <v>0.09194013734823128</v>
+        <v>0.0919401373482313</v>
       </c>
       <c r="D121">
-        <v>0.04805144829905356</v>
+        <v>0.04805144829905357</v>
       </c>
       <c r="E121">
         <v>4.8</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.05778492255252875</v>
+        <v>-0.05778492255252879</v>
       </c>
       <c r="D122">
-        <v>0.0302006207363042</v>
+        <v>0.03020062073630422</v>
       </c>
       <c r="E122">
         <v>3</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.2305084165030664</v>
+        <v>0.2305084165030667</v>
       </c>
     </row>
     <row r="3">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.14996541181677</v>
+        <v>0.1499654118167697</v>
       </c>
     </row>
     <row r="5">
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.1038665802183321</v>
+        <v>0.103866580218332</v>
       </c>
     </row>
     <row r="6">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.08234530798454653</v>
+        <v>0.08234530798454655</v>
       </c>
     </row>
     <row r="7">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.0675865024045315</v>
+        <v>0.06758650240453153</v>
       </c>
     </row>
     <row r="8">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.05696365144440953</v>
+        <v>0.05696365144440959</v>
       </c>
     </row>
     <row r="9">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.04863834718557119</v>
+        <v>0.04863834718557117</v>
       </c>
     </row>
     <row r="10">
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.03852204713698768</v>
+        <v>0.03852204713698763</v>
       </c>
     </row>
     <row r="11">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.03649043900496065</v>
+        <v>0.03649043900496068</v>
       </c>
     </row>
     <row r="12">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.01359199013855183</v>
+        <v>0.01359199013855185</v>
       </c>
     </row>
   </sheetData>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.4279701372342439</v>
+        <v>-0.4279701372342429</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.4277317691593429</v>
+        <v>-0.4277317691593427</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.4217763905429527</v>
+        <v>0.4217763905429536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.3479836458610875</v>
+        <v>-0.3479836458610874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.3068382714595461</v>
+        <v>0.306838271459547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.2821037769312924</v>
+        <v>-0.2821037769312917</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.0872433337405719</v>
+        <v>-0.08724333374057207</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.07712735392209487</v>
+        <v>-0.07712735392209447</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.03261335495786311</v>
+        <v>-0.03261335495786359</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.5686319028350156</v>
+        <v>-0.5686319028350157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.4175107227959658</v>
+        <v>-0.4175107227959651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.4089882430616423</v>
+        <v>-0.4089882430616426</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.27564179511722</v>
+        <v>-0.2756417951172191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.2729876985051061</v>
+        <v>0.272987698505105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.2609491248307983</v>
+        <v>-0.2609491248307991</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.257546166379183</v>
+        <v>-0.2575461663791829</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.1990559648130767</v>
+        <v>0.1990559648130769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.08620369356542516</v>
+        <v>0.08620369356542434</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.05457360636486595</v>
+        <v>-0.05457360636486649</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
